--- a/VerveStacks_DEU/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_DEU/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FAD049E2-DE92-43D1-A4A6-985F5A380D5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7E96DB67-6DF3-4FF2-987D-39B28006F12F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -97,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1536" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1536" uniqueCount="93">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -294,9 +294,6 @@
     <t>UCE_max nuclear capacity</t>
   </si>
   <si>
-    <t>UC_RHSRT~2050</t>
-  </si>
-  <si>
     <t>life</t>
   </si>
   <si>
@@ -357,6 +354,12 @@
     <t>wind*</t>
   </si>
   <si>
+    <t>~UC_T: 2050</t>
+  </si>
+  <si>
+    <t>base-year nuclear capacity</t>
+  </si>
+  <si>
     <t>geothermal</t>
   </si>
   <si>
@@ -382,7 +385,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -432,8 +435,24 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -450,6 +469,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -480,13 +504,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -497,10 +522,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="4"/>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
     <cellStyle name="Heading 3" xfId="2" builtinId="18"/>
     <cellStyle name="Heading 4" xfId="3" builtinId="19"/>
+    <cellStyle name="Neutral" xfId="4" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
@@ -969,7 +997,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C6" t="s">
         <v>7</v>
@@ -979,7 +1007,7 @@
         <v/>
       </c>
       <c r="F6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
@@ -998,7 +1026,7 @@
     </row>
     <row r="7" spans="1:38" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
@@ -1236,7 +1264,7 @@
     </row>
     <row r="11" spans="1:38" ht="14.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
@@ -1249,7 +1277,7 @@
     </row>
     <row r="12" spans="1:38" x14ac:dyDescent="0.45">
       <c r="F12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G12" s="3">
         <v>0.13646444879321595</v>
@@ -1269,7 +1297,7 @@
         <v>26</v>
       </c>
       <c r="U13" t="s">
-        <v>10</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:38" x14ac:dyDescent="0.45">
@@ -1309,9 +1337,6 @@
       <c r="AC14" t="s">
         <v>17</v>
       </c>
-      <c r="AD14" t="s">
-        <v>65</v>
-      </c>
     </row>
     <row r="15" spans="1:38" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
@@ -1325,7 +1350,7 @@
         <v>Hydropower - large-scale unit,Solar photovoltaics - Large scale unit,Wind offshore,Wind onshore</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="U15" t="s">
         <v>64</v>
@@ -1337,15 +1362,18 @@
         <v>1</v>
       </c>
       <c r="AB15">
+        <f>AE15*2.5</f>
+        <v>10.5</v>
+      </c>
+      <c r="AC15">
+        <v>3</v>
+      </c>
+      <c r="AE15" s="11">
         <f>SUMIFS(historical_data_long!$D$3:$D$626,historical_data_long!$A$3:$A$626,Veda!$V15,historical_data_long!$C$3:$C$626,"GW",historical_data_long!$B$3:$B$626,2022)</f>
         <v>4.2</v>
       </c>
-      <c r="AC15">
-        <v>3</v>
-      </c>
-      <c r="AD15">
-        <f>AB15*2.5</f>
-        <v>10.5</v>
+      <c r="AF15" s="10" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:38" x14ac:dyDescent="0.45">
@@ -1487,24 +1515,24 @@
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E28">
         <v>50</v>
       </c>
       <c r="G28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E29">
         <v>8.76</v>
       </c>
       <c r="G29" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.45">
@@ -1567,7 +1595,7 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.45">
       <c r="D40" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E40">
         <v>-1</v>
@@ -1575,7 +1603,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1598,41 +1627,41 @@
   <sheetData>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C10" t="s">
+        <v>69</v>
+      </c>
+      <c r="D10" t="s">
         <v>70</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>71</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>72</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>73</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>74</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>75</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>76</v>
-      </c>
-      <c r="J10" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1666,7 +1695,7 @@
     </row>
     <row r="18" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B18" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -1674,16 +1703,16 @@
         <v>48</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>2</v>
       </c>
       <c r="D19" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" s="8" t="s">
         <v>79</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>80</v>
       </c>
       <c r="F19" s="8">
         <v>2025</v>
@@ -1708,7 +1737,7 @@
         <v>solar</v>
       </c>
       <c r="D20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -1738,7 +1767,7 @@
         <v>wind*</v>
       </c>
       <c r="D21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -1768,7 +1797,7 @@
         <v>hydro</v>
       </c>
       <c r="D22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -1798,7 +1827,7 @@
         <v>nuclear</v>
       </c>
       <c r="D23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -1953,7 +1982,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B10">
         <v>2000</v>
@@ -2079,7 +2108,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B19">
         <v>2001</v>
@@ -2205,7 +2234,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B28">
         <v>2002</v>
@@ -2331,7 +2360,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B37">
         <v>2003</v>
@@ -2457,7 +2486,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B46">
         <v>2004</v>
@@ -2583,7 +2612,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B55">
         <v>2005</v>
@@ -2709,7 +2738,7 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B64">
         <v>2006</v>
@@ -2835,7 +2864,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B73">
         <v>2007</v>
@@ -2961,7 +2990,7 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B82">
         <v>2008</v>
@@ -3087,7 +3116,7 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B91">
         <v>2009</v>
@@ -3213,7 +3242,7 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B100">
         <v>2010</v>
@@ -3339,7 +3368,7 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B109">
         <v>2011</v>
@@ -3465,7 +3494,7 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B118">
         <v>2012</v>
@@ -3591,7 +3620,7 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B127">
         <v>2013</v>
@@ -3717,7 +3746,7 @@
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B136">
         <v>2014</v>
@@ -3843,7 +3872,7 @@
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B145">
         <v>2015</v>
@@ -3969,7 +3998,7 @@
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B154">
         <v>2016</v>
@@ -4095,7 +4124,7 @@
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B163">
         <v>2017</v>
@@ -4221,7 +4250,7 @@
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B172">
         <v>2018</v>
@@ -4347,7 +4376,7 @@
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B181">
         <v>2019</v>
@@ -4473,7 +4502,7 @@
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B190">
         <v>2020</v>
@@ -4599,7 +4628,7 @@
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A199" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B199">
         <v>2021</v>
@@ -4725,7 +4754,7 @@
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A208" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B208">
         <v>2022</v>
@@ -4851,7 +4880,7 @@
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A217" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B217">
         <v>2023</v>
@@ -4977,7 +5006,7 @@
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A226" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B226">
         <v>2000</v>
@@ -5103,7 +5132,7 @@
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A235" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B235">
         <v>2001</v>
@@ -5229,7 +5258,7 @@
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A244" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B244">
         <v>2002</v>
@@ -5355,7 +5384,7 @@
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A253" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B253">
         <v>2003</v>
@@ -5481,7 +5510,7 @@
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A262" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B262">
         <v>2004</v>
@@ -5607,7 +5636,7 @@
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A271" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B271">
         <v>2005</v>
@@ -5733,7 +5762,7 @@
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A280" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B280">
         <v>2006</v>
@@ -5859,7 +5888,7 @@
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A289" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B289">
         <v>2007</v>
@@ -5985,7 +6014,7 @@
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A298" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B298">
         <v>2008</v>
@@ -6111,7 +6140,7 @@
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A307" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B307">
         <v>2009</v>
@@ -6237,7 +6266,7 @@
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A316" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B316">
         <v>2010</v>
@@ -6363,7 +6392,7 @@
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A325" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B325">
         <v>2011</v>
@@ -6489,7 +6518,7 @@
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A334" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B334">
         <v>2012</v>
@@ -6615,7 +6644,7 @@
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A343" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B343">
         <v>2013</v>
@@ -6741,7 +6770,7 @@
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A352" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B352">
         <v>2014</v>
@@ -6867,7 +6896,7 @@
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A361" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B361">
         <v>2015</v>
@@ -6993,7 +7022,7 @@
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A370" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B370">
         <v>2016</v>
@@ -7119,7 +7148,7 @@
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A379" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B379">
         <v>2017</v>
@@ -7245,7 +7274,7 @@
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A388" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B388">
         <v>2018</v>
@@ -7371,7 +7400,7 @@
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A397" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B397">
         <v>2019</v>
@@ -7497,7 +7526,7 @@
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A406" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B406">
         <v>2020</v>
@@ -7623,7 +7652,7 @@
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A415" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B415">
         <v>2021</v>
@@ -7749,7 +7778,7 @@
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A424" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B424">
         <v>2022</v>
@@ -7875,7 +7904,7 @@
     </row>
     <row r="433" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A433" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B433">
         <v>2023</v>
@@ -8001,7 +8030,7 @@
     </row>
     <row r="442" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A442" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B442">
         <v>2000</v>
@@ -8127,7 +8156,7 @@
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A451" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B451">
         <v>2001</v>
@@ -8253,7 +8282,7 @@
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A460" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B460">
         <v>2002</v>
@@ -8379,7 +8408,7 @@
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A469" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B469">
         <v>2003</v>
@@ -8505,7 +8534,7 @@
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A478" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B478">
         <v>2004</v>
@@ -8631,7 +8660,7 @@
     </row>
     <row r="487" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A487" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B487">
         <v>2005</v>
@@ -8757,7 +8786,7 @@
     </row>
     <row r="496" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A496" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B496">
         <v>2006</v>
@@ -8883,7 +8912,7 @@
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A505" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B505">
         <v>2007</v>
@@ -9009,7 +9038,7 @@
     </row>
     <row r="514" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A514" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B514">
         <v>2008</v>
@@ -9135,7 +9164,7 @@
     </row>
     <row r="523" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A523" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B523">
         <v>2009</v>
@@ -9261,7 +9290,7 @@
     </row>
     <row r="532" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A532" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B532">
         <v>2010</v>
@@ -9387,7 +9416,7 @@
     </row>
     <row r="541" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A541" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B541">
         <v>2011</v>
@@ -9513,7 +9542,7 @@
     </row>
     <row r="550" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A550" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B550">
         <v>2012</v>
@@ -9639,7 +9668,7 @@
     </row>
     <row r="559" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A559" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B559">
         <v>2013</v>
@@ -9765,7 +9794,7 @@
     </row>
     <row r="568" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A568" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B568">
         <v>2014</v>
@@ -9891,7 +9920,7 @@
     </row>
     <row r="577" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A577" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B577">
         <v>2015</v>
@@ -10017,7 +10046,7 @@
     </row>
     <row r="586" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A586" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B586">
         <v>2016</v>
@@ -10143,7 +10172,7 @@
     </row>
     <row r="595" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A595" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B595">
         <v>2017</v>
@@ -10269,7 +10298,7 @@
     </row>
     <row r="604" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A604" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B604">
         <v>2018</v>
@@ -10395,7 +10424,7 @@
     </row>
     <row r="613" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A613" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B613">
         <v>2019</v>
@@ -10521,7 +10550,7 @@
     </row>
     <row r="622" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A622" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B622">
         <v>2020</v>
@@ -10647,7 +10676,7 @@
     </row>
     <row r="631" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A631" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B631">
         <v>2021</v>
@@ -10773,7 +10802,7 @@
     </row>
     <row r="640" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A640" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B640">
         <v>2022</v>
@@ -10899,7 +10928,7 @@
     </row>
     <row r="649" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A649" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B649">
         <v>2023</v>

--- a/VerveStacks_DEU/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_DEU/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7E96DB67-6DF3-4FF2-987D-39B28006F12F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E51B91EE-DA69-4F0E-A98F-81AE736FAA07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_DEU/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_DEU/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E51B91EE-DA69-4F0E-A98F-81AE736FAA07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1EE9FA29-4C84-4E26-966C-197345EB37B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_DEU/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_DEU/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1EE9FA29-4C84-4E26-966C-197345EB37B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{640BD78B-56AC-47D7-B0CE-101047524127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_DEU/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_DEU/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{640BD78B-56AC-47D7-B0CE-101047524127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB246602-9365-46BE-B4D5-C763B49B8AC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_DEU/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_DEU/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB246602-9365-46BE-B4D5-C763B49B8AC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EEB8510C-845F-4EC1-9326-71C26C0AA3EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_DEU/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_DEU/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EEB8510C-845F-4EC1-9326-71C26C0AA3EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB8449BD-B6A2-4EA2-A1B0-73F9A56DC52F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_DEU/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_DEU/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB8449BD-B6A2-4EA2-A1B0-73F9A56DC52F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8E892840-C9CB-414B-9A52-85CC953F5205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_DEU/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_DEU/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8E892840-C9CB-414B-9A52-85CC953F5205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BAE973C7-E675-464E-B2DA-746774C12B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,6 +40,32 @@
     <author>Amit Kanudia</author>
   </authors>
   <commentList>
+    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{2FF9EF2B-EBD7-4C7E-9F26-8FF1228838F5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Amit Kanudia:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+11-09-2025
+AFS will be sufficient
+</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D8" authorId="0" shapeId="0" xr:uid="{79577DE7-359E-49C1-A1D9-EC64BAD436CB}">
       <text>
         <r>
@@ -97,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1536" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1536" uniqueCount="94">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -358,6 +384,9 @@
   </si>
   <si>
     <t>base-year nuclear capacity</t>
+  </si>
+  <si>
+    <t>\I: hydro</t>
   </si>
   <si>
     <t>geothermal</t>
@@ -971,15 +1000,12 @@
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
-        <v>6</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="4">
-        <f>IFERROR(VLOOKUP(B5,$F$3:$J$11,5,FALSE),"")</f>
-        <v>0.33171570735303152</v>
-      </c>
+      <c r="D5" s="4"/>
       <c r="F5" t="s">
         <v>8</v>
       </c>
@@ -1007,7 +1033,7 @@
         <v/>
       </c>
       <c r="F6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
@@ -1264,7 +1290,7 @@
     </row>
     <row r="11" spans="1:38" ht="14.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
@@ -1277,7 +1303,7 @@
     </row>
     <row r="12" spans="1:38" x14ac:dyDescent="0.45">
       <c r="F12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G12" s="3">
         <v>0.13646444879321595</v>
@@ -1627,12 +1653,12 @@
   <sheetData>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C10" t="s">
         <v>69</v>
@@ -1661,7 +1687,7 @@
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1982,7 +2008,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B10">
         <v>2000</v>
@@ -2108,7 +2134,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B19">
         <v>2001</v>
@@ -2234,7 +2260,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B28">
         <v>2002</v>
@@ -2360,7 +2386,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B37">
         <v>2003</v>
@@ -2486,7 +2512,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B46">
         <v>2004</v>
@@ -2612,7 +2638,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B55">
         <v>2005</v>
@@ -2738,7 +2764,7 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B64">
         <v>2006</v>
@@ -2864,7 +2890,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B73">
         <v>2007</v>
@@ -2990,7 +3016,7 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B82">
         <v>2008</v>
@@ -3116,7 +3142,7 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B91">
         <v>2009</v>
@@ -3242,7 +3268,7 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B100">
         <v>2010</v>
@@ -3368,7 +3394,7 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B109">
         <v>2011</v>
@@ -3494,7 +3520,7 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B118">
         <v>2012</v>
@@ -3620,7 +3646,7 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B127">
         <v>2013</v>
@@ -3746,7 +3772,7 @@
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B136">
         <v>2014</v>
@@ -3872,7 +3898,7 @@
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B145">
         <v>2015</v>
@@ -3998,7 +4024,7 @@
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B154">
         <v>2016</v>
@@ -4124,7 +4150,7 @@
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B163">
         <v>2017</v>
@@ -4250,7 +4276,7 @@
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B172">
         <v>2018</v>
@@ -4376,7 +4402,7 @@
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B181">
         <v>2019</v>
@@ -4502,7 +4528,7 @@
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B190">
         <v>2020</v>
@@ -4628,7 +4654,7 @@
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A199" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B199">
         <v>2021</v>
@@ -4754,7 +4780,7 @@
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A208" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B208">
         <v>2022</v>
@@ -4880,7 +4906,7 @@
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A217" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B217">
         <v>2023</v>
@@ -5006,7 +5032,7 @@
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A226" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B226">
         <v>2000</v>
@@ -5132,7 +5158,7 @@
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A235" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B235">
         <v>2001</v>
@@ -5258,7 +5284,7 @@
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A244" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B244">
         <v>2002</v>
@@ -5384,7 +5410,7 @@
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A253" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B253">
         <v>2003</v>
@@ -5510,7 +5536,7 @@
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A262" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B262">
         <v>2004</v>
@@ -5636,7 +5662,7 @@
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A271" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B271">
         <v>2005</v>
@@ -5762,7 +5788,7 @@
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A280" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B280">
         <v>2006</v>
@@ -5888,7 +5914,7 @@
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A289" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B289">
         <v>2007</v>
@@ -6014,7 +6040,7 @@
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A298" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B298">
         <v>2008</v>
@@ -6140,7 +6166,7 @@
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A307" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B307">
         <v>2009</v>
@@ -6266,7 +6292,7 @@
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A316" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B316">
         <v>2010</v>
@@ -6392,7 +6418,7 @@
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A325" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B325">
         <v>2011</v>
@@ -6518,7 +6544,7 @@
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A334" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B334">
         <v>2012</v>
@@ -6644,7 +6670,7 @@
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A343" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B343">
         <v>2013</v>
@@ -6770,7 +6796,7 @@
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A352" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B352">
         <v>2014</v>
@@ -6896,7 +6922,7 @@
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A361" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B361">
         <v>2015</v>
@@ -7022,7 +7048,7 @@
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A370" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B370">
         <v>2016</v>
@@ -7148,7 +7174,7 @@
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A379" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B379">
         <v>2017</v>
@@ -7274,7 +7300,7 @@
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A388" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B388">
         <v>2018</v>
@@ -7400,7 +7426,7 @@
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A397" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B397">
         <v>2019</v>
@@ -7526,7 +7552,7 @@
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A406" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B406">
         <v>2020</v>
@@ -7652,7 +7678,7 @@
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A415" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B415">
         <v>2021</v>
@@ -7778,7 +7804,7 @@
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A424" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B424">
         <v>2022</v>
@@ -7904,7 +7930,7 @@
     </row>
     <row r="433" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A433" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B433">
         <v>2023</v>
@@ -8030,7 +8056,7 @@
     </row>
     <row r="442" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A442" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B442">
         <v>2000</v>
@@ -8156,7 +8182,7 @@
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A451" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B451">
         <v>2001</v>
@@ -8282,7 +8308,7 @@
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A460" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B460">
         <v>2002</v>
@@ -8408,7 +8434,7 @@
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A469" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B469">
         <v>2003</v>
@@ -8534,7 +8560,7 @@
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A478" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B478">
         <v>2004</v>
@@ -8660,7 +8686,7 @@
     </row>
     <row r="487" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A487" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B487">
         <v>2005</v>
@@ -8786,7 +8812,7 @@
     </row>
     <row r="496" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A496" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B496">
         <v>2006</v>
@@ -8912,7 +8938,7 @@
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A505" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B505">
         <v>2007</v>
@@ -9038,7 +9064,7 @@
     </row>
     <row r="514" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A514" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B514">
         <v>2008</v>
@@ -9164,7 +9190,7 @@
     </row>
     <row r="523" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A523" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B523">
         <v>2009</v>
@@ -9290,7 +9316,7 @@
     </row>
     <row r="532" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A532" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B532">
         <v>2010</v>
@@ -9416,7 +9442,7 @@
     </row>
     <row r="541" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A541" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B541">
         <v>2011</v>
@@ -9542,7 +9568,7 @@
     </row>
     <row r="550" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A550" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B550">
         <v>2012</v>
@@ -9668,7 +9694,7 @@
     </row>
     <row r="559" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A559" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B559">
         <v>2013</v>
@@ -9794,7 +9820,7 @@
     </row>
     <row r="568" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A568" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B568">
         <v>2014</v>
@@ -9920,7 +9946,7 @@
     </row>
     <row r="577" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A577" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B577">
         <v>2015</v>
@@ -10046,7 +10072,7 @@
     </row>
     <row r="586" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A586" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B586">
         <v>2016</v>
@@ -10172,7 +10198,7 @@
     </row>
     <row r="595" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A595" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B595">
         <v>2017</v>
@@ -10298,7 +10324,7 @@
     </row>
     <row r="604" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A604" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B604">
         <v>2018</v>
@@ -10424,7 +10450,7 @@
     </row>
     <row r="613" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A613" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B613">
         <v>2019</v>
@@ -10550,7 +10576,7 @@
     </row>
     <row r="622" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A622" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B622">
         <v>2020</v>
@@ -10676,7 +10702,7 @@
     </row>
     <row r="631" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A631" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B631">
         <v>2021</v>
@@ -10802,7 +10828,7 @@
     </row>
     <row r="640" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A640" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B640">
         <v>2022</v>
@@ -10928,7 +10954,7 @@
     </row>
     <row r="649" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A649" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B649">
         <v>2023</v>

--- a/VerveStacks_DEU/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_DEU/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BAE973C7-E675-464E-B2DA-746774C12B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C5F2D450-1B68-4EAB-ACAF-30F5D1371077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_DEU/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_DEU/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C5F2D450-1B68-4EAB-ACAF-30F5D1371077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0997F37E-CE51-4E5C-9AAA-B1CEEE4AA53F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_DEU/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_DEU/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0997F37E-CE51-4E5C-9AAA-B1CEEE4AA53F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F95C34A-575D-4D2B-B875-76A9BCBE05F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_DEU/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_DEU/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F95C34A-575D-4D2B-B875-76A9BCBE05F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{73AF4A65-5DE2-42FC-B6D9-3C0A21A77FE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_DEU/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_DEU/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{73AF4A65-5DE2-42FC-B6D9-3C0A21A77FE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2ED0155-9914-4E3A-9C25-FBF8A6D91F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_DEU/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_DEU/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2ED0155-9914-4E3A-9C25-FBF8A6D91F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9FEFE27F-92B2-4EFF-879E-C420EA4A152D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_DEU/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_DEU/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9FEFE27F-92B2-4EFF-879E-C420EA4A152D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{771E9579-3758-4877-9EB7-E8FA74EA2618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_DEU/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_DEU/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{771E9579-3758-4877-9EB7-E8FA74EA2618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E5053F49-2AA2-4EFF-AD18-5A34B75E9F9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_DEU/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_DEU/SuppXLS/Scen_Base_VS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E5053F49-2AA2-4EFF-AD18-5A34B75E9F9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D30D70B8-A374-4FBD-8025-5017173D9E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_DEU/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_DEU/SuppXLS/Scen_Base_VS.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{29F2CD94-FF8D-4379-B80A-C3B1DD06932D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{02A47B79-A499-4B69-A0EA-C39E80B8F6FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Veda" sheetId="1" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="5" r:id="rId2"/>
+    <sheet name="re_targets" sheetId="5" r:id="rId1"/>
+    <sheet name="Veda" sheetId="1" r:id="rId2"/>
     <sheet name="buildrates" sheetId="4" r:id="rId3"/>
     <sheet name="historical_data_long" sheetId="3" r:id="rId4"/>
   </sheets>
@@ -124,7 +124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2072" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2074" uniqueCount="140">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -390,6 +390,9 @@
     <t>\I: hydro</t>
   </si>
   <si>
+    <t>UCE_min oil fleet utilization</t>
+  </si>
+  <si>
     <t>geothermal</t>
   </si>
   <si>
@@ -551,8 +554,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -680,7 +684,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -693,6 +697,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="4"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1034,6 +1039,861 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DF7586B-197A-4D3B-8C43-4C506543C837}">
+  <dimension ref="B9:L33"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B10" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" t="s">
+        <v>94</v>
+      </c>
+      <c r="D10" t="s">
+        <v>95</v>
+      </c>
+      <c r="E10" t="s">
+        <v>96</v>
+      </c>
+      <c r="F10" t="s">
+        <v>97</v>
+      </c>
+      <c r="G10" t="s">
+        <v>98</v>
+      </c>
+      <c r="H10" t="s">
+        <v>99</v>
+      </c>
+      <c r="I10" t="s">
+        <v>100</v>
+      </c>
+      <c r="J10" t="s">
+        <v>101</v>
+      </c>
+      <c r="K10" t="s">
+        <v>102</v>
+      </c>
+      <c r="L10" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="99.75" x14ac:dyDescent="0.45">
+      <c r="B11">
+        <v>2030</v>
+      </c>
+      <c r="C11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E11">
+        <v>30</v>
+      </c>
+      <c r="F11" t="s">
+        <v>106</v>
+      </c>
+      <c r="G11" t="s">
+        <v>107</v>
+      </c>
+      <c r="H11" t="s">
+        <v>108</v>
+      </c>
+      <c r="I11" s="13">
+        <v>45528</v>
+      </c>
+      <c r="J11" t="s">
+        <v>109</v>
+      </c>
+      <c r="K11" t="s">
+        <v>110</v>
+      </c>
+      <c r="L11" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="99.75" x14ac:dyDescent="0.45">
+      <c r="B12">
+        <v>2030</v>
+      </c>
+      <c r="C12" t="s">
+        <v>112</v>
+      </c>
+      <c r="D12" t="s">
+        <v>105</v>
+      </c>
+      <c r="E12">
+        <v>115</v>
+      </c>
+      <c r="F12" t="s">
+        <v>106</v>
+      </c>
+      <c r="G12" t="s">
+        <v>107</v>
+      </c>
+      <c r="H12" t="s">
+        <v>108</v>
+      </c>
+      <c r="I12" s="13">
+        <v>45528</v>
+      </c>
+      <c r="J12" t="s">
+        <v>109</v>
+      </c>
+      <c r="K12" t="s">
+        <v>110</v>
+      </c>
+      <c r="L12" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="99.75" x14ac:dyDescent="0.45">
+      <c r="B13">
+        <v>2030</v>
+      </c>
+      <c r="C13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D13" t="s">
+        <v>105</v>
+      </c>
+      <c r="E13">
+        <v>215</v>
+      </c>
+      <c r="F13" t="s">
+        <v>106</v>
+      </c>
+      <c r="G13" t="s">
+        <v>107</v>
+      </c>
+      <c r="H13" t="s">
+        <v>108</v>
+      </c>
+      <c r="I13" s="13">
+        <v>45528</v>
+      </c>
+      <c r="J13" t="s">
+        <v>109</v>
+      </c>
+      <c r="K13" t="s">
+        <v>110</v>
+      </c>
+      <c r="L13" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="99.75" x14ac:dyDescent="0.45">
+      <c r="B14">
+        <v>2030</v>
+      </c>
+      <c r="C14" t="s">
+        <v>114</v>
+      </c>
+      <c r="D14" t="s">
+        <v>115</v>
+      </c>
+      <c r="E14">
+        <v>600</v>
+      </c>
+      <c r="F14" t="s">
+        <v>106</v>
+      </c>
+      <c r="G14" t="s">
+        <v>107</v>
+      </c>
+      <c r="H14" t="s">
+        <v>108</v>
+      </c>
+      <c r="I14" s="13">
+        <v>45528</v>
+      </c>
+      <c r="J14" t="s">
+        <v>109</v>
+      </c>
+      <c r="K14" t="s">
+        <v>110</v>
+      </c>
+      <c r="L14" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="99.75" x14ac:dyDescent="0.45">
+      <c r="B15">
+        <v>2030</v>
+      </c>
+      <c r="C15" t="s">
+        <v>114</v>
+      </c>
+      <c r="D15" t="s">
+        <v>116</v>
+      </c>
+      <c r="E15">
+        <v>80</v>
+      </c>
+      <c r="F15" t="s">
+        <v>106</v>
+      </c>
+      <c r="G15" t="s">
+        <v>107</v>
+      </c>
+      <c r="H15" t="s">
+        <v>108</v>
+      </c>
+      <c r="I15" s="13">
+        <v>45528</v>
+      </c>
+      <c r="J15" t="s">
+        <v>109</v>
+      </c>
+      <c r="K15" t="s">
+        <v>110</v>
+      </c>
+      <c r="L15" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B16">
+        <v>2030</v>
+      </c>
+      <c r="C16" t="s">
+        <v>117</v>
+      </c>
+      <c r="D16" t="s">
+        <v>105</v>
+      </c>
+      <c r="E16">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="F16" t="s">
+        <v>118</v>
+      </c>
+      <c r="G16" t="s">
+        <v>119</v>
+      </c>
+      <c r="H16" t="s">
+        <v>120</v>
+      </c>
+      <c r="I16" s="13">
+        <v>44866</v>
+      </c>
+      <c r="J16" t="s">
+        <v>121</v>
+      </c>
+      <c r="K16" t="s">
+        <v>122</v>
+      </c>
+      <c r="L16" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B17">
+        <v>2040</v>
+      </c>
+      <c r="C17" t="s">
+        <v>117</v>
+      </c>
+      <c r="D17" t="s">
+        <v>105</v>
+      </c>
+      <c r="E17">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="F17" t="s">
+        <v>118</v>
+      </c>
+      <c r="G17" t="s">
+        <v>119</v>
+      </c>
+      <c r="H17" t="s">
+        <v>120</v>
+      </c>
+      <c r="I17" s="13">
+        <v>44866</v>
+      </c>
+      <c r="J17" t="s">
+        <v>121</v>
+      </c>
+      <c r="K17" t="s">
+        <v>122</v>
+      </c>
+      <c r="L17" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B18">
+        <v>2045</v>
+      </c>
+      <c r="C18" t="s">
+        <v>117</v>
+      </c>
+      <c r="D18" t="s">
+        <v>105</v>
+      </c>
+      <c r="E18">
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="F18" t="s">
+        <v>118</v>
+      </c>
+      <c r="G18" t="s">
+        <v>119</v>
+      </c>
+      <c r="H18" t="s">
+        <v>120</v>
+      </c>
+      <c r="I18" s="13">
+        <v>44866</v>
+      </c>
+      <c r="J18" t="s">
+        <v>121</v>
+      </c>
+      <c r="K18" t="s">
+        <v>122</v>
+      </c>
+      <c r="L18" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B19">
+        <v>2030</v>
+      </c>
+      <c r="C19" t="s">
+        <v>124</v>
+      </c>
+      <c r="D19" t="s">
+        <v>105</v>
+      </c>
+      <c r="E19">
+        <v>5.2</v>
+      </c>
+      <c r="F19" t="s">
+        <v>118</v>
+      </c>
+      <c r="G19" t="s">
+        <v>119</v>
+      </c>
+      <c r="H19" t="s">
+        <v>120</v>
+      </c>
+      <c r="I19" s="13">
+        <v>44866</v>
+      </c>
+      <c r="J19" t="s">
+        <v>121</v>
+      </c>
+      <c r="K19" t="s">
+        <v>122</v>
+      </c>
+      <c r="L19" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B20">
+        <v>2040</v>
+      </c>
+      <c r="C20" t="s">
+        <v>124</v>
+      </c>
+      <c r="D20" t="s">
+        <v>105</v>
+      </c>
+      <c r="E20">
+        <v>5.2</v>
+      </c>
+      <c r="F20" t="s">
+        <v>118</v>
+      </c>
+      <c r="G20" t="s">
+        <v>119</v>
+      </c>
+      <c r="H20" t="s">
+        <v>120</v>
+      </c>
+      <c r="I20" s="13">
+        <v>44866</v>
+      </c>
+      <c r="J20" t="s">
+        <v>121</v>
+      </c>
+      <c r="K20" t="s">
+        <v>122</v>
+      </c>
+      <c r="L20" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B21">
+        <v>2045</v>
+      </c>
+      <c r="C21" t="s">
+        <v>124</v>
+      </c>
+      <c r="D21" t="s">
+        <v>105</v>
+      </c>
+      <c r="E21">
+        <v>5.2</v>
+      </c>
+      <c r="F21" t="s">
+        <v>118</v>
+      </c>
+      <c r="G21" t="s">
+        <v>119</v>
+      </c>
+      <c r="H21" t="s">
+        <v>120</v>
+      </c>
+      <c r="I21" s="13">
+        <v>44866</v>
+      </c>
+      <c r="J21" t="s">
+        <v>121</v>
+      </c>
+      <c r="K21" t="s">
+        <v>122</v>
+      </c>
+      <c r="L21" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B22">
+        <v>2040</v>
+      </c>
+      <c r="C22" t="s">
+        <v>104</v>
+      </c>
+      <c r="D22" t="s">
+        <v>105</v>
+      </c>
+      <c r="E22">
+        <v>70</v>
+      </c>
+      <c r="F22" t="s">
+        <v>118</v>
+      </c>
+      <c r="G22" t="s">
+        <v>119</v>
+      </c>
+      <c r="H22" t="s">
+        <v>120</v>
+      </c>
+      <c r="I22" s="13">
+        <v>44866</v>
+      </c>
+      <c r="J22" t="s">
+        <v>121</v>
+      </c>
+      <c r="K22" t="s">
+        <v>122</v>
+      </c>
+      <c r="L22" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B23">
+        <v>2045</v>
+      </c>
+      <c r="C23" t="s">
+        <v>104</v>
+      </c>
+      <c r="D23" t="s">
+        <v>105</v>
+      </c>
+      <c r="E23">
+        <v>70</v>
+      </c>
+      <c r="F23" t="s">
+        <v>118</v>
+      </c>
+      <c r="G23" t="s">
+        <v>119</v>
+      </c>
+      <c r="H23" t="s">
+        <v>120</v>
+      </c>
+      <c r="I23" s="13">
+        <v>44866</v>
+      </c>
+      <c r="J23" t="s">
+        <v>121</v>
+      </c>
+      <c r="K23" t="s">
+        <v>122</v>
+      </c>
+      <c r="L23" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B24">
+        <v>2040</v>
+      </c>
+      <c r="C24" t="s">
+        <v>112</v>
+      </c>
+      <c r="D24" t="s">
+        <v>105</v>
+      </c>
+      <c r="E24">
+        <v>160</v>
+      </c>
+      <c r="F24" t="s">
+        <v>118</v>
+      </c>
+      <c r="G24" t="s">
+        <v>119</v>
+      </c>
+      <c r="H24" t="s">
+        <v>120</v>
+      </c>
+      <c r="I24" s="13">
+        <v>44866</v>
+      </c>
+      <c r="J24" t="s">
+        <v>121</v>
+      </c>
+      <c r="K24" t="s">
+        <v>122</v>
+      </c>
+      <c r="L24" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B25">
+        <v>2045</v>
+      </c>
+      <c r="C25" t="s">
+        <v>112</v>
+      </c>
+      <c r="D25" t="s">
+        <v>105</v>
+      </c>
+      <c r="E25">
+        <v>160</v>
+      </c>
+      <c r="F25" t="s">
+        <v>118</v>
+      </c>
+      <c r="G25" t="s">
+        <v>119</v>
+      </c>
+      <c r="H25" t="s">
+        <v>120</v>
+      </c>
+      <c r="I25" s="13">
+        <v>44866</v>
+      </c>
+      <c r="J25" t="s">
+        <v>121</v>
+      </c>
+      <c r="K25" t="s">
+        <v>122</v>
+      </c>
+      <c r="L25" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B26">
+        <v>2040</v>
+      </c>
+      <c r="C26" t="s">
+        <v>113</v>
+      </c>
+      <c r="D26" t="s">
+        <v>105</v>
+      </c>
+      <c r="E26">
+        <v>400</v>
+      </c>
+      <c r="F26" t="s">
+        <v>118</v>
+      </c>
+      <c r="G26" t="s">
+        <v>119</v>
+      </c>
+      <c r="H26" t="s">
+        <v>120</v>
+      </c>
+      <c r="I26" s="13">
+        <v>44866</v>
+      </c>
+      <c r="J26" t="s">
+        <v>121</v>
+      </c>
+      <c r="K26" t="s">
+        <v>122</v>
+      </c>
+      <c r="L26" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B27">
+        <v>2045</v>
+      </c>
+      <c r="C27" t="s">
+        <v>113</v>
+      </c>
+      <c r="D27" t="s">
+        <v>105</v>
+      </c>
+      <c r="E27">
+        <v>428.2</v>
+      </c>
+      <c r="F27" t="s">
+        <v>118</v>
+      </c>
+      <c r="G27" t="s">
+        <v>119</v>
+      </c>
+      <c r="H27" t="s">
+        <v>120</v>
+      </c>
+      <c r="I27" s="13">
+        <v>44866</v>
+      </c>
+      <c r="J27" t="s">
+        <v>121</v>
+      </c>
+      <c r="K27" t="s">
+        <v>122</v>
+      </c>
+      <c r="L27" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B28">
+        <v>2030</v>
+      </c>
+      <c r="C28" t="s">
+        <v>114</v>
+      </c>
+      <c r="D28" t="s">
+        <v>125</v>
+      </c>
+      <c r="E28">
+        <v>75</v>
+      </c>
+      <c r="F28" t="s">
+        <v>118</v>
+      </c>
+      <c r="G28" t="s">
+        <v>126</v>
+      </c>
+      <c r="H28" t="s">
+        <v>127</v>
+      </c>
+      <c r="I28" s="13">
+        <v>44986</v>
+      </c>
+      <c r="J28" t="s">
+        <v>128</v>
+      </c>
+      <c r="K28" t="s">
+        <v>129</v>
+      </c>
+      <c r="L28" s="14" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B29">
+        <v>2030</v>
+      </c>
+      <c r="C29" t="s">
+        <v>104</v>
+      </c>
+      <c r="D29" t="s">
+        <v>105</v>
+      </c>
+      <c r="E29">
+        <v>30.5</v>
+      </c>
+      <c r="F29" t="s">
+        <v>131</v>
+      </c>
+      <c r="G29" t="s">
+        <v>132</v>
+      </c>
+      <c r="H29" t="s">
+        <v>133</v>
+      </c>
+      <c r="I29" s="13">
+        <v>44652</v>
+      </c>
+      <c r="J29" t="s">
+        <v>134</v>
+      </c>
+      <c r="K29" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="L29" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B30">
+        <v>2030</v>
+      </c>
+      <c r="C30" t="s">
+        <v>112</v>
+      </c>
+      <c r="D30" t="s">
+        <v>105</v>
+      </c>
+      <c r="E30">
+        <v>115</v>
+      </c>
+      <c r="F30" t="s">
+        <v>131</v>
+      </c>
+      <c r="G30" t="s">
+        <v>132</v>
+      </c>
+      <c r="H30" t="s">
+        <v>133</v>
+      </c>
+      <c r="I30" s="13">
+        <v>44652</v>
+      </c>
+      <c r="J30" t="s">
+        <v>134</v>
+      </c>
+      <c r="K30" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="L30" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B31">
+        <v>2030</v>
+      </c>
+      <c r="C31" t="s">
+        <v>113</v>
+      </c>
+      <c r="D31" t="s">
+        <v>105</v>
+      </c>
+      <c r="E31">
+        <v>215</v>
+      </c>
+      <c r="F31" t="s">
+        <v>131</v>
+      </c>
+      <c r="G31" t="s">
+        <v>132</v>
+      </c>
+      <c r="H31" t="s">
+        <v>133</v>
+      </c>
+      <c r="I31" s="13">
+        <v>44652</v>
+      </c>
+      <c r="J31" t="s">
+        <v>134</v>
+      </c>
+      <c r="K31" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="L31" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B32">
+        <v>2030</v>
+      </c>
+      <c r="C32" t="s">
+        <v>114</v>
+      </c>
+      <c r="D32" t="s">
+        <v>115</v>
+      </c>
+      <c r="E32">
+        <v>600</v>
+      </c>
+      <c r="F32" t="s">
+        <v>131</v>
+      </c>
+      <c r="G32" t="s">
+        <v>132</v>
+      </c>
+      <c r="H32" t="s">
+        <v>133</v>
+      </c>
+      <c r="I32" s="13">
+        <v>44652</v>
+      </c>
+      <c r="J32" t="s">
+        <v>134</v>
+      </c>
+      <c r="K32" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="L32" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B33">
+        <v>2030</v>
+      </c>
+      <c r="C33" t="s">
+        <v>114</v>
+      </c>
+      <c r="D33" t="s">
+        <v>116</v>
+      </c>
+      <c r="E33">
+        <v>80</v>
+      </c>
+      <c r="F33" t="s">
+        <v>131</v>
+      </c>
+      <c r="G33" t="s">
+        <v>132</v>
+      </c>
+      <c r="H33" t="s">
+        <v>133</v>
+      </c>
+      <c r="I33" s="13">
+        <v>44652</v>
+      </c>
+      <c r="J33" t="s">
+        <v>134</v>
+      </c>
+      <c r="K33" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="L33" t="s">
+        <v>136</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AL40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -1064,7 +1924,7 @@
     <col min="33" max="33" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="7" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="7.86328125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="4.73046875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="5.265625" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="9.19921875" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="11.19921875" bestFit="1" customWidth="1"/>
   </cols>
@@ -1177,7 +2037,7 @@
         <v/>
       </c>
       <c r="F6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
@@ -1431,10 +2291,34 @@
       <c r="J10" s="3">
         <v>0.11452491530550409</v>
       </c>
+      <c r="AF10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>23</v>
+      </c>
+      <c r="AH10">
+        <f>-1/8.76</f>
+        <v>-0.11415525114155252</v>
+      </c>
+      <c r="AI10" s="2">
+        <f>VLOOKUP(AG10,$F$3:$J$11,2,FALSE)</f>
+        <v>1.4374104995812058</v>
+      </c>
+      <c r="AJ10" s="12">
+        <f>AI10*$AD$1</f>
+        <v>0.28748209991624118</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:38" ht="14.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
@@ -1447,7 +2331,7 @@
     </row>
     <row r="12" spans="1:38" x14ac:dyDescent="0.45">
       <c r="F12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G12" s="3">
         <v>0.13646444879321595</v>
@@ -1775,861 +2659,6 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C68860C9-300B-4257-B876-A0CD42C4E98C}">
-  <dimension ref="B9:L33"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B9" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B10" t="s">
-        <v>92</v>
-      </c>
-      <c r="C10" t="s">
-        <v>93</v>
-      </c>
-      <c r="D10" t="s">
-        <v>94</v>
-      </c>
-      <c r="E10" t="s">
-        <v>95</v>
-      </c>
-      <c r="F10" t="s">
-        <v>96</v>
-      </c>
-      <c r="G10" t="s">
-        <v>97</v>
-      </c>
-      <c r="H10" t="s">
-        <v>98</v>
-      </c>
-      <c r="I10" t="s">
-        <v>99</v>
-      </c>
-      <c r="J10" t="s">
-        <v>100</v>
-      </c>
-      <c r="K10" t="s">
-        <v>101</v>
-      </c>
-      <c r="L10" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" ht="99.75" x14ac:dyDescent="0.45">
-      <c r="B11">
-        <v>2030</v>
-      </c>
-      <c r="C11" t="s">
-        <v>103</v>
-      </c>
-      <c r="D11" t="s">
-        <v>104</v>
-      </c>
-      <c r="E11">
-        <v>30</v>
-      </c>
-      <c r="F11" t="s">
-        <v>105</v>
-      </c>
-      <c r="G11" t="s">
-        <v>106</v>
-      </c>
-      <c r="H11" t="s">
-        <v>107</v>
-      </c>
-      <c r="I11" s="12">
-        <v>45528</v>
-      </c>
-      <c r="J11" t="s">
-        <v>108</v>
-      </c>
-      <c r="K11" t="s">
-        <v>109</v>
-      </c>
-      <c r="L11" s="13" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" ht="99.75" x14ac:dyDescent="0.45">
-      <c r="B12">
-        <v>2030</v>
-      </c>
-      <c r="C12" t="s">
-        <v>111</v>
-      </c>
-      <c r="D12" t="s">
-        <v>104</v>
-      </c>
-      <c r="E12">
-        <v>115</v>
-      </c>
-      <c r="F12" t="s">
-        <v>105</v>
-      </c>
-      <c r="G12" t="s">
-        <v>106</v>
-      </c>
-      <c r="H12" t="s">
-        <v>107</v>
-      </c>
-      <c r="I12" s="12">
-        <v>45528</v>
-      </c>
-      <c r="J12" t="s">
-        <v>108</v>
-      </c>
-      <c r="K12" t="s">
-        <v>109</v>
-      </c>
-      <c r="L12" s="13" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" ht="99.75" x14ac:dyDescent="0.45">
-      <c r="B13">
-        <v>2030</v>
-      </c>
-      <c r="C13" t="s">
-        <v>112</v>
-      </c>
-      <c r="D13" t="s">
-        <v>104</v>
-      </c>
-      <c r="E13">
-        <v>215</v>
-      </c>
-      <c r="F13" t="s">
-        <v>105</v>
-      </c>
-      <c r="G13" t="s">
-        <v>106</v>
-      </c>
-      <c r="H13" t="s">
-        <v>107</v>
-      </c>
-      <c r="I13" s="12">
-        <v>45528</v>
-      </c>
-      <c r="J13" t="s">
-        <v>108</v>
-      </c>
-      <c r="K13" t="s">
-        <v>109</v>
-      </c>
-      <c r="L13" s="13" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" ht="99.75" x14ac:dyDescent="0.45">
-      <c r="B14">
-        <v>2030</v>
-      </c>
-      <c r="C14" t="s">
-        <v>113</v>
-      </c>
-      <c r="D14" t="s">
-        <v>114</v>
-      </c>
-      <c r="E14">
-        <v>600</v>
-      </c>
-      <c r="F14" t="s">
-        <v>105</v>
-      </c>
-      <c r="G14" t="s">
-        <v>106</v>
-      </c>
-      <c r="H14" t="s">
-        <v>107</v>
-      </c>
-      <c r="I14" s="12">
-        <v>45528</v>
-      </c>
-      <c r="J14" t="s">
-        <v>108</v>
-      </c>
-      <c r="K14" t="s">
-        <v>109</v>
-      </c>
-      <c r="L14" s="13" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" ht="99.75" x14ac:dyDescent="0.45">
-      <c r="B15">
-        <v>2030</v>
-      </c>
-      <c r="C15" t="s">
-        <v>113</v>
-      </c>
-      <c r="D15" t="s">
-        <v>115</v>
-      </c>
-      <c r="E15">
-        <v>80</v>
-      </c>
-      <c r="F15" t="s">
-        <v>105</v>
-      </c>
-      <c r="G15" t="s">
-        <v>106</v>
-      </c>
-      <c r="H15" t="s">
-        <v>107</v>
-      </c>
-      <c r="I15" s="12">
-        <v>45528</v>
-      </c>
-      <c r="J15" t="s">
-        <v>108</v>
-      </c>
-      <c r="K15" t="s">
-        <v>109</v>
-      </c>
-      <c r="L15" s="13" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B16">
-        <v>2030</v>
-      </c>
-      <c r="C16" t="s">
-        <v>116</v>
-      </c>
-      <c r="D16" t="s">
-        <v>104</v>
-      </c>
-      <c r="E16">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="F16" t="s">
-        <v>117</v>
-      </c>
-      <c r="G16" t="s">
-        <v>118</v>
-      </c>
-      <c r="H16" t="s">
-        <v>119</v>
-      </c>
-      <c r="I16" s="12">
-        <v>44866</v>
-      </c>
-      <c r="J16" t="s">
-        <v>120</v>
-      </c>
-      <c r="K16" t="s">
-        <v>121</v>
-      </c>
-      <c r="L16" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B17">
-        <v>2040</v>
-      </c>
-      <c r="C17" t="s">
-        <v>116</v>
-      </c>
-      <c r="D17" t="s">
-        <v>104</v>
-      </c>
-      <c r="E17">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="F17" t="s">
-        <v>117</v>
-      </c>
-      <c r="G17" t="s">
-        <v>118</v>
-      </c>
-      <c r="H17" t="s">
-        <v>119</v>
-      </c>
-      <c r="I17" s="12">
-        <v>44866</v>
-      </c>
-      <c r="J17" t="s">
-        <v>120</v>
-      </c>
-      <c r="K17" t="s">
-        <v>121</v>
-      </c>
-      <c r="L17" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B18">
-        <v>2045</v>
-      </c>
-      <c r="C18" t="s">
-        <v>116</v>
-      </c>
-      <c r="D18" t="s">
-        <v>104</v>
-      </c>
-      <c r="E18">
-        <v>2.4300000000000002</v>
-      </c>
-      <c r="F18" t="s">
-        <v>117</v>
-      </c>
-      <c r="G18" t="s">
-        <v>118</v>
-      </c>
-      <c r="H18" t="s">
-        <v>119</v>
-      </c>
-      <c r="I18" s="12">
-        <v>44866</v>
-      </c>
-      <c r="J18" t="s">
-        <v>120</v>
-      </c>
-      <c r="K18" t="s">
-        <v>121</v>
-      </c>
-      <c r="L18" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B19">
-        <v>2030</v>
-      </c>
-      <c r="C19" t="s">
-        <v>123</v>
-      </c>
-      <c r="D19" t="s">
-        <v>104</v>
-      </c>
-      <c r="E19">
-        <v>5.2</v>
-      </c>
-      <c r="F19" t="s">
-        <v>117</v>
-      </c>
-      <c r="G19" t="s">
-        <v>118</v>
-      </c>
-      <c r="H19" t="s">
-        <v>119</v>
-      </c>
-      <c r="I19" s="12">
-        <v>44866</v>
-      </c>
-      <c r="J19" t="s">
-        <v>120</v>
-      </c>
-      <c r="K19" t="s">
-        <v>121</v>
-      </c>
-      <c r="L19" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B20">
-        <v>2040</v>
-      </c>
-      <c r="C20" t="s">
-        <v>123</v>
-      </c>
-      <c r="D20" t="s">
-        <v>104</v>
-      </c>
-      <c r="E20">
-        <v>5.2</v>
-      </c>
-      <c r="F20" t="s">
-        <v>117</v>
-      </c>
-      <c r="G20" t="s">
-        <v>118</v>
-      </c>
-      <c r="H20" t="s">
-        <v>119</v>
-      </c>
-      <c r="I20" s="12">
-        <v>44866</v>
-      </c>
-      <c r="J20" t="s">
-        <v>120</v>
-      </c>
-      <c r="K20" t="s">
-        <v>121</v>
-      </c>
-      <c r="L20" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B21">
-        <v>2045</v>
-      </c>
-      <c r="C21" t="s">
-        <v>123</v>
-      </c>
-      <c r="D21" t="s">
-        <v>104</v>
-      </c>
-      <c r="E21">
-        <v>5.2</v>
-      </c>
-      <c r="F21" t="s">
-        <v>117</v>
-      </c>
-      <c r="G21" t="s">
-        <v>118</v>
-      </c>
-      <c r="H21" t="s">
-        <v>119</v>
-      </c>
-      <c r="I21" s="12">
-        <v>44866</v>
-      </c>
-      <c r="J21" t="s">
-        <v>120</v>
-      </c>
-      <c r="K21" t="s">
-        <v>121</v>
-      </c>
-      <c r="L21" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B22">
-        <v>2040</v>
-      </c>
-      <c r="C22" t="s">
-        <v>103</v>
-      </c>
-      <c r="D22" t="s">
-        <v>104</v>
-      </c>
-      <c r="E22">
-        <v>70</v>
-      </c>
-      <c r="F22" t="s">
-        <v>117</v>
-      </c>
-      <c r="G22" t="s">
-        <v>118</v>
-      </c>
-      <c r="H22" t="s">
-        <v>119</v>
-      </c>
-      <c r="I22" s="12">
-        <v>44866</v>
-      </c>
-      <c r="J22" t="s">
-        <v>120</v>
-      </c>
-      <c r="K22" t="s">
-        <v>121</v>
-      </c>
-      <c r="L22" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B23">
-        <v>2045</v>
-      </c>
-      <c r="C23" t="s">
-        <v>103</v>
-      </c>
-      <c r="D23" t="s">
-        <v>104</v>
-      </c>
-      <c r="E23">
-        <v>70</v>
-      </c>
-      <c r="F23" t="s">
-        <v>117</v>
-      </c>
-      <c r="G23" t="s">
-        <v>118</v>
-      </c>
-      <c r="H23" t="s">
-        <v>119</v>
-      </c>
-      <c r="I23" s="12">
-        <v>44866</v>
-      </c>
-      <c r="J23" t="s">
-        <v>120</v>
-      </c>
-      <c r="K23" t="s">
-        <v>121</v>
-      </c>
-      <c r="L23" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B24">
-        <v>2040</v>
-      </c>
-      <c r="C24" t="s">
-        <v>111</v>
-      </c>
-      <c r="D24" t="s">
-        <v>104</v>
-      </c>
-      <c r="E24">
-        <v>160</v>
-      </c>
-      <c r="F24" t="s">
-        <v>117</v>
-      </c>
-      <c r="G24" t="s">
-        <v>118</v>
-      </c>
-      <c r="H24" t="s">
-        <v>119</v>
-      </c>
-      <c r="I24" s="12">
-        <v>44866</v>
-      </c>
-      <c r="J24" t="s">
-        <v>120</v>
-      </c>
-      <c r="K24" t="s">
-        <v>121</v>
-      </c>
-      <c r="L24" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B25">
-        <v>2045</v>
-      </c>
-      <c r="C25" t="s">
-        <v>111</v>
-      </c>
-      <c r="D25" t="s">
-        <v>104</v>
-      </c>
-      <c r="E25">
-        <v>160</v>
-      </c>
-      <c r="F25" t="s">
-        <v>117</v>
-      </c>
-      <c r="G25" t="s">
-        <v>118</v>
-      </c>
-      <c r="H25" t="s">
-        <v>119</v>
-      </c>
-      <c r="I25" s="12">
-        <v>44866</v>
-      </c>
-      <c r="J25" t="s">
-        <v>120</v>
-      </c>
-      <c r="K25" t="s">
-        <v>121</v>
-      </c>
-      <c r="L25" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B26">
-        <v>2040</v>
-      </c>
-      <c r="C26" t="s">
-        <v>112</v>
-      </c>
-      <c r="D26" t="s">
-        <v>104</v>
-      </c>
-      <c r="E26">
-        <v>400</v>
-      </c>
-      <c r="F26" t="s">
-        <v>117</v>
-      </c>
-      <c r="G26" t="s">
-        <v>118</v>
-      </c>
-      <c r="H26" t="s">
-        <v>119</v>
-      </c>
-      <c r="I26" s="12">
-        <v>44866</v>
-      </c>
-      <c r="J26" t="s">
-        <v>120</v>
-      </c>
-      <c r="K26" t="s">
-        <v>121</v>
-      </c>
-      <c r="L26" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B27">
-        <v>2045</v>
-      </c>
-      <c r="C27" t="s">
-        <v>112</v>
-      </c>
-      <c r="D27" t="s">
-        <v>104</v>
-      </c>
-      <c r="E27">
-        <v>428.2</v>
-      </c>
-      <c r="F27" t="s">
-        <v>117</v>
-      </c>
-      <c r="G27" t="s">
-        <v>118</v>
-      </c>
-      <c r="H27" t="s">
-        <v>119</v>
-      </c>
-      <c r="I27" s="12">
-        <v>44866</v>
-      </c>
-      <c r="J27" t="s">
-        <v>120</v>
-      </c>
-      <c r="K27" t="s">
-        <v>121</v>
-      </c>
-      <c r="L27" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="28" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B28">
-        <v>2030</v>
-      </c>
-      <c r="C28" t="s">
-        <v>113</v>
-      </c>
-      <c r="D28" t="s">
-        <v>124</v>
-      </c>
-      <c r="E28">
-        <v>75</v>
-      </c>
-      <c r="F28" t="s">
-        <v>117</v>
-      </c>
-      <c r="G28" t="s">
-        <v>125</v>
-      </c>
-      <c r="H28" t="s">
-        <v>126</v>
-      </c>
-      <c r="I28" s="12">
-        <v>44986</v>
-      </c>
-      <c r="J28" t="s">
-        <v>127</v>
-      </c>
-      <c r="K28" t="s">
-        <v>128</v>
-      </c>
-      <c r="L28" s="13" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="29" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B29">
-        <v>2030</v>
-      </c>
-      <c r="C29" t="s">
-        <v>103</v>
-      </c>
-      <c r="D29" t="s">
-        <v>104</v>
-      </c>
-      <c r="E29">
-        <v>30.5</v>
-      </c>
-      <c r="F29" t="s">
-        <v>130</v>
-      </c>
-      <c r="G29" t="s">
-        <v>131</v>
-      </c>
-      <c r="H29" t="s">
-        <v>132</v>
-      </c>
-      <c r="I29" s="12">
-        <v>44652</v>
-      </c>
-      <c r="J29" t="s">
-        <v>133</v>
-      </c>
-      <c r="K29" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="L29" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="30" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B30">
-        <v>2030</v>
-      </c>
-      <c r="C30" t="s">
-        <v>111</v>
-      </c>
-      <c r="D30" t="s">
-        <v>104</v>
-      </c>
-      <c r="E30">
-        <v>115</v>
-      </c>
-      <c r="F30" t="s">
-        <v>130</v>
-      </c>
-      <c r="G30" t="s">
-        <v>131</v>
-      </c>
-      <c r="H30" t="s">
-        <v>132</v>
-      </c>
-      <c r="I30" s="12">
-        <v>44652</v>
-      </c>
-      <c r="J30" t="s">
-        <v>133</v>
-      </c>
-      <c r="K30" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="L30" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="31" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B31">
-        <v>2030</v>
-      </c>
-      <c r="C31" t="s">
-        <v>112</v>
-      </c>
-      <c r="D31" t="s">
-        <v>104</v>
-      </c>
-      <c r="E31">
-        <v>215</v>
-      </c>
-      <c r="F31" t="s">
-        <v>130</v>
-      </c>
-      <c r="G31" t="s">
-        <v>131</v>
-      </c>
-      <c r="H31" t="s">
-        <v>132</v>
-      </c>
-      <c r="I31" s="12">
-        <v>44652</v>
-      </c>
-      <c r="J31" t="s">
-        <v>133</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="L31" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="32" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B32">
-        <v>2030</v>
-      </c>
-      <c r="C32" t="s">
-        <v>113</v>
-      </c>
-      <c r="D32" t="s">
-        <v>114</v>
-      </c>
-      <c r="E32">
-        <v>600</v>
-      </c>
-      <c r="F32" t="s">
-        <v>130</v>
-      </c>
-      <c r="G32" t="s">
-        <v>131</v>
-      </c>
-      <c r="H32" t="s">
-        <v>132</v>
-      </c>
-      <c r="I32" s="12">
-        <v>44652</v>
-      </c>
-      <c r="J32" t="s">
-        <v>133</v>
-      </c>
-      <c r="K32" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="L32" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="33" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B33">
-        <v>2030</v>
-      </c>
-      <c r="C33" t="s">
-        <v>113</v>
-      </c>
-      <c r="D33" t="s">
-        <v>115</v>
-      </c>
-      <c r="E33">
-        <v>80</v>
-      </c>
-      <c r="F33" t="s">
-        <v>130</v>
-      </c>
-      <c r="G33" t="s">
-        <v>131</v>
-      </c>
-      <c r="H33" t="s">
-        <v>132</v>
-      </c>
-      <c r="I33" s="12">
-        <v>44652</v>
-      </c>
-      <c r="J33" t="s">
-        <v>133</v>
-      </c>
-      <c r="K33" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="L33" t="s">
-        <v>135</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -2652,12 +2681,12 @@
   <sheetData>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C10" t="s">
         <v>69</v>
@@ -2686,7 +2715,7 @@
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C11">
         <v>15</v>
@@ -6367,7 +6396,7 @@
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A250" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B250">
         <v>2000</v>
@@ -6493,7 +6522,7 @@
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A259" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B259">
         <v>2001</v>
@@ -6619,7 +6648,7 @@
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A268" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B268">
         <v>2002</v>
@@ -6745,7 +6774,7 @@
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A277" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B277">
         <v>2003</v>
@@ -6871,7 +6900,7 @@
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A286" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B286">
         <v>2004</v>
@@ -6997,7 +7026,7 @@
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A295" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B295">
         <v>2005</v>
@@ -7123,7 +7152,7 @@
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A304" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B304">
         <v>2006</v>
@@ -7249,7 +7278,7 @@
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A313" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B313">
         <v>2007</v>
@@ -7375,7 +7404,7 @@
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A322" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B322">
         <v>2008</v>
@@ -7501,7 +7530,7 @@
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A331" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B331">
         <v>2009</v>
@@ -7627,7 +7656,7 @@
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A340" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B340">
         <v>2010</v>
@@ -7753,7 +7782,7 @@
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A349" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B349">
         <v>2011</v>
@@ -7879,7 +7908,7 @@
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A358" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B358">
         <v>2012</v>
@@ -8005,7 +8034,7 @@
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A367" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B367">
         <v>2013</v>
@@ -8131,7 +8160,7 @@
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A376" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B376">
         <v>2014</v>
@@ -8257,7 +8286,7 @@
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A385" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B385">
         <v>2015</v>
@@ -8383,7 +8412,7 @@
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A394" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B394">
         <v>2016</v>
@@ -8509,7 +8538,7 @@
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A403" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B403">
         <v>2017</v>
@@ -8635,7 +8664,7 @@
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A412" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B412">
         <v>2018</v>
@@ -8761,7 +8790,7 @@
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A421" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B421">
         <v>2019</v>
@@ -8887,7 +8916,7 @@
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A430" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B430">
         <v>2020</v>
@@ -9013,7 +9042,7 @@
     </row>
     <row r="439" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A439" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B439">
         <v>2021</v>
@@ -9139,7 +9168,7 @@
     </row>
     <row r="448" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A448" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B448">
         <v>2022</v>
@@ -9265,7 +9294,7 @@
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A457" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B457">
         <v>2023</v>
@@ -10091,7 +10120,7 @@
     </row>
     <row r="516" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A516" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B516">
         <v>2018</v>
@@ -10105,7 +10134,7 @@
     </row>
     <row r="517" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A517" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B517">
         <v>2019</v>
@@ -10119,7 +10148,7 @@
     </row>
     <row r="518" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A518" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B518">
         <v>2020</v>
@@ -10133,7 +10162,7 @@
     </row>
     <row r="519" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A519" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B519">
         <v>2021</v>
@@ -10147,7 +10176,7 @@
     </row>
     <row r="520" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A520" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B520">
         <v>2022</v>
@@ -10161,7 +10190,7 @@
     </row>
     <row r="521" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A521" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B521">
         <v>2023</v>
@@ -10175,7 +10204,7 @@
     </row>
     <row r="522" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A522" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B522">
         <v>2024</v>
@@ -10189,7 +10218,7 @@
     </row>
     <row r="523" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A523" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B523">
         <v>2011</v>
@@ -10203,7 +10232,7 @@
     </row>
     <row r="524" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A524" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B524">
         <v>2012</v>
@@ -10217,7 +10246,7 @@
     </row>
     <row r="525" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A525" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B525">
         <v>2013</v>
@@ -10231,7 +10260,7 @@
     </row>
     <row r="526" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A526" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B526">
         <v>2014</v>
@@ -10245,7 +10274,7 @@
     </row>
     <row r="527" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A527" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B527">
         <v>2015</v>
@@ -10259,7 +10288,7 @@
     </row>
     <row r="528" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A528" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B528">
         <v>2016</v>
@@ -10273,7 +10302,7 @@
     </row>
     <row r="529" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A529" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B529">
         <v>2017</v>
@@ -10287,7 +10316,7 @@
     </row>
     <row r="530" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A530" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B530">
         <v>2004</v>
@@ -10301,7 +10330,7 @@
     </row>
     <row r="531" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A531" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B531">
         <v>2005</v>
@@ -10315,7 +10344,7 @@
     </row>
     <row r="532" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A532" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B532">
         <v>2006</v>
@@ -10329,7 +10358,7 @@
     </row>
     <row r="533" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A533" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B533">
         <v>2007</v>
@@ -10343,7 +10372,7 @@
     </row>
     <row r="534" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A534" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B534">
         <v>2008</v>
@@ -10357,7 +10386,7 @@
     </row>
     <row r="535" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A535" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B535">
         <v>2009</v>
@@ -10371,7 +10400,7 @@
     </row>
     <row r="536" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A536" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B536">
         <v>2010</v>
@@ -10385,7 +10414,7 @@
     </row>
     <row r="537" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A537" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B537">
         <v>2000</v>
@@ -10399,7 +10428,7 @@
     </row>
     <row r="538" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A538" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B538">
         <v>2001</v>
@@ -10413,7 +10442,7 @@
     </row>
     <row r="539" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A539" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B539">
         <v>2002</v>
@@ -10427,7 +10456,7 @@
     </row>
     <row r="540" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A540" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B540">
         <v>2003</v>
@@ -10441,7 +10470,7 @@
     </row>
     <row r="541" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A541" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B541">
         <v>2002</v>
@@ -10455,7 +10484,7 @@
     </row>
     <row r="542" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A542" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B542">
         <v>2003</v>
@@ -10469,7 +10498,7 @@
     </row>
     <row r="543" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A543" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B543">
         <v>2004</v>
@@ -10483,7 +10512,7 @@
     </row>
     <row r="544" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A544" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B544">
         <v>2005</v>
@@ -10497,7 +10526,7 @@
     </row>
     <row r="545" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A545" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B545">
         <v>2006</v>
@@ -10511,7 +10540,7 @@
     </row>
     <row r="546" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A546" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B546">
         <v>2007</v>
@@ -10525,7 +10554,7 @@
     </row>
     <row r="547" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A547" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B547">
         <v>2008</v>
@@ -10539,7 +10568,7 @@
     </row>
     <row r="548" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A548" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B548">
         <v>2009</v>
@@ -10553,7 +10582,7 @@
     </row>
     <row r="549" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A549" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B549">
         <v>2010</v>
@@ -10567,7 +10596,7 @@
     </row>
     <row r="550" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A550" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B550">
         <v>2011</v>
@@ -10581,7 +10610,7 @@
     </row>
     <row r="551" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A551" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B551">
         <v>2012</v>
@@ -10595,7 +10624,7 @@
     </row>
     <row r="552" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A552" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B552">
         <v>2013</v>
@@ -10609,7 +10638,7 @@
     </row>
     <row r="553" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A553" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B553">
         <v>2014</v>
@@ -10623,7 +10652,7 @@
     </row>
     <row r="554" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A554" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B554">
         <v>2015</v>
@@ -10637,7 +10666,7 @@
     </row>
     <row r="555" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A555" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B555">
         <v>2016</v>
@@ -10651,7 +10680,7 @@
     </row>
     <row r="556" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A556" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B556">
         <v>2017</v>
@@ -10665,7 +10694,7 @@
     </row>
     <row r="557" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A557" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B557">
         <v>2018</v>
@@ -10679,7 +10708,7 @@
     </row>
     <row r="558" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A558" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B558">
         <v>2019</v>
@@ -10693,7 +10722,7 @@
     </row>
     <row r="559" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A559" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B559">
         <v>2020</v>
@@ -10707,7 +10736,7 @@
     </row>
     <row r="560" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A560" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B560">
         <v>2021</v>
@@ -10721,7 +10750,7 @@
     </row>
     <row r="561" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A561" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B561">
         <v>2022</v>
@@ -10735,7 +10764,7 @@
     </row>
     <row r="562" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A562" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B562">
         <v>2000</v>
@@ -10749,7 +10778,7 @@
     </row>
     <row r="563" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A563" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B563">
         <v>2001</v>
@@ -10763,7 +10792,7 @@
     </row>
     <row r="564" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A564" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B564">
         <v>2018</v>
@@ -10777,7 +10806,7 @@
     </row>
     <row r="565" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A565" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B565">
         <v>2019</v>
@@ -10791,7 +10820,7 @@
     </row>
     <row r="566" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A566" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B566">
         <v>2020</v>
@@ -10805,7 +10834,7 @@
     </row>
     <row r="567" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A567" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B567">
         <v>2021</v>
@@ -10819,7 +10848,7 @@
     </row>
     <row r="568" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A568" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B568">
         <v>2022</v>
@@ -10833,7 +10862,7 @@
     </row>
     <row r="569" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A569" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B569">
         <v>2023</v>
@@ -10847,7 +10876,7 @@
     </row>
     <row r="570" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A570" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B570">
         <v>2024</v>
@@ -10861,7 +10890,7 @@
     </row>
     <row r="571" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A571" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B571">
         <v>2011</v>
@@ -10875,7 +10904,7 @@
     </row>
     <row r="572" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A572" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B572">
         <v>2012</v>
@@ -10889,7 +10918,7 @@
     </row>
     <row r="573" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A573" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B573">
         <v>2013</v>
@@ -10903,7 +10932,7 @@
     </row>
     <row r="574" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A574" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B574">
         <v>2014</v>
@@ -10917,7 +10946,7 @@
     </row>
     <row r="575" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A575" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B575">
         <v>2015</v>
@@ -10931,7 +10960,7 @@
     </row>
     <row r="576" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A576" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B576">
         <v>2016</v>
@@ -10945,7 +10974,7 @@
     </row>
     <row r="577" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A577" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B577">
         <v>2017</v>
@@ -10959,7 +10988,7 @@
     </row>
     <row r="578" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A578" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B578">
         <v>2009</v>
@@ -10973,7 +11002,7 @@
     </row>
     <row r="579" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A579" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B579">
         <v>2010</v>
@@ -10987,7 +11016,7 @@
     </row>
     <row r="580" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A580" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B580">
         <v>2009</v>
@@ -11001,7 +11030,7 @@
     </row>
     <row r="581" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A581" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B581">
         <v>2010</v>
@@ -11015,7 +11044,7 @@
     </row>
     <row r="582" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A582" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B582">
         <v>2011</v>
@@ -11029,7 +11058,7 @@
     </row>
     <row r="583" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A583" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B583">
         <v>2012</v>
@@ -11043,7 +11072,7 @@
     </row>
     <row r="584" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A584" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B584">
         <v>2013</v>
@@ -11057,7 +11086,7 @@
     </row>
     <row r="585" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A585" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B585">
         <v>2014</v>
@@ -11071,7 +11100,7 @@
     </row>
     <row r="586" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A586" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B586">
         <v>2015</v>
@@ -11085,7 +11114,7 @@
     </row>
     <row r="587" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A587" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B587">
         <v>2016</v>
@@ -11099,7 +11128,7 @@
     </row>
     <row r="588" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A588" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B588">
         <v>2017</v>
@@ -11113,7 +11142,7 @@
     </row>
     <row r="589" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A589" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B589">
         <v>2018</v>
@@ -11127,7 +11156,7 @@
     </row>
     <row r="590" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A590" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B590">
         <v>2019</v>
@@ -11141,7 +11170,7 @@
     </row>
     <row r="591" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A591" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B591">
         <v>2020</v>
@@ -11155,7 +11184,7 @@
     </row>
     <row r="592" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A592" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B592">
         <v>2021</v>
@@ -11169,7 +11198,7 @@
     </row>
     <row r="593" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A593" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B593">
         <v>2022</v>
@@ -13843,7 +13872,7 @@
     </row>
     <row r="784" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A784" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B784">
         <v>2018</v>
@@ -13857,7 +13886,7 @@
     </row>
     <row r="785" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A785" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B785">
         <v>2019</v>
@@ -13871,7 +13900,7 @@
     </row>
     <row r="786" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A786" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B786">
         <v>2020</v>
@@ -13885,7 +13914,7 @@
     </row>
     <row r="787" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A787" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B787">
         <v>2021</v>
@@ -13899,7 +13928,7 @@
     </row>
     <row r="788" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A788" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B788">
         <v>2022</v>
@@ -13913,7 +13942,7 @@
     </row>
     <row r="789" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A789" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B789">
         <v>2023</v>
@@ -13927,7 +13956,7 @@
     </row>
     <row r="790" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A790" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B790">
         <v>2024</v>
@@ -13941,7 +13970,7 @@
     </row>
     <row r="791" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A791" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B791">
         <v>2011</v>
@@ -13955,7 +13984,7 @@
     </row>
     <row r="792" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A792" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B792">
         <v>2012</v>
@@ -13969,7 +13998,7 @@
     </row>
     <row r="793" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A793" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B793">
         <v>2013</v>
@@ -13983,7 +14012,7 @@
     </row>
     <row r="794" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A794" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B794">
         <v>2014</v>
@@ -13997,7 +14026,7 @@
     </row>
     <row r="795" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A795" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B795">
         <v>2015</v>
@@ -14011,7 +14040,7 @@
     </row>
     <row r="796" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A796" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B796">
         <v>2016</v>
@@ -14025,7 +14054,7 @@
     </row>
     <row r="797" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A797" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B797">
         <v>2017</v>
@@ -14039,7 +14068,7 @@
     </row>
     <row r="798" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A798" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B798">
         <v>2004</v>
@@ -14053,7 +14082,7 @@
     </row>
     <row r="799" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A799" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B799">
         <v>2005</v>
@@ -14067,7 +14096,7 @@
     </row>
     <row r="800" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A800" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B800">
         <v>2006</v>
@@ -14081,7 +14110,7 @@
     </row>
     <row r="801" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A801" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B801">
         <v>2007</v>
@@ -14095,7 +14124,7 @@
     </row>
     <row r="802" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A802" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B802">
         <v>2008</v>
@@ -14109,7 +14138,7 @@
     </row>
     <row r="803" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A803" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B803">
         <v>2009</v>
@@ -14123,7 +14152,7 @@
     </row>
     <row r="804" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A804" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B804">
         <v>2010</v>
@@ -14137,7 +14166,7 @@
     </row>
     <row r="805" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A805" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B805">
         <v>2008</v>
@@ -14151,7 +14180,7 @@
     </row>
     <row r="806" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A806" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B806">
         <v>2009</v>
@@ -14165,7 +14194,7 @@
     </row>
     <row r="807" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A807" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B807">
         <v>2010</v>
@@ -14179,7 +14208,7 @@
     </row>
     <row r="808" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A808" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B808">
         <v>2011</v>
@@ -14193,7 +14222,7 @@
     </row>
     <row r="809" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A809" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B809">
         <v>2012</v>
@@ -14207,7 +14236,7 @@
     </row>
     <row r="810" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A810" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B810">
         <v>2013</v>
@@ -14221,7 +14250,7 @@
     </row>
     <row r="811" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A811" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B811">
         <v>2014</v>
@@ -14235,7 +14264,7 @@
     </row>
     <row r="812" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A812" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B812">
         <v>2015</v>
@@ -14249,7 +14278,7 @@
     </row>
     <row r="813" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A813" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B813">
         <v>2016</v>
@@ -14263,7 +14292,7 @@
     </row>
     <row r="814" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A814" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B814">
         <v>2017</v>
@@ -14277,7 +14306,7 @@
     </row>
     <row r="815" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A815" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B815">
         <v>2018</v>
@@ -14291,7 +14320,7 @@
     </row>
     <row r="816" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A816" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B816">
         <v>2019</v>
@@ -14305,7 +14334,7 @@
     </row>
     <row r="817" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A817" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B817">
         <v>2020</v>
@@ -14319,7 +14348,7 @@
     </row>
     <row r="818" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A818" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B818">
         <v>2021</v>
@@ -14333,7 +14362,7 @@
     </row>
     <row r="819" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A819" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B819">
         <v>2022</v>

--- a/VerveStacks_DEU/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_DEU/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{02A47B79-A499-4B69-A0EA-C39E80B8F6FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C413A31-DC63-4D12-A051-E6BD31114F48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1039,7 +1039,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DF7586B-197A-4D3B-8C43-4C506543C837}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{029DE1B7-1CB4-455B-B0AA-18CEEE5B29B8}">
   <dimension ref="B9:L33"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
